--- a/employee_surveys/031_employee_compensation_benchmarking_application_form--employee_surveys.xlsx
+++ b/employee_surveys/031_employee_compensation_benchmarking_application_form--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>What is your job title?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>salary_range</t>
+          <t>What is your salary range?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>years_of_service</t>
+          <t>How many years of service have you had in your current company?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>benefits_packages</t>
+          <t>What type of benefits packages do you currently have?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>company_size</t>
+          <t>What is the size of your company?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>department prophets</t>
+          <t>What department do you currently work in?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>manager_title</t>
+          <t>What is your manager's title?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>employee_id</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>What is your date of birth?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>When did you start working for this company?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>When did you leave this company?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Do you have any additional notes or comments?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>job_responsibilities</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>Can you describe your current job responsibilities?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,80 +847,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>Can you provide your manager's name?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>job_title_1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>job_title</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>job_title_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>job_title</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>job_title_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>job_title</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
